--- a/static/files/financement.xlsx
+++ b/static/files/financement.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolasoudard/workspace/beta.gouv.fr/apilos/static/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ayoub.bouchachia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762975EC-3214-904C-AAA5-0B56EA998315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{982554E2-5205-4DF0-BC2E-FDA66B29DB4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1420" yWindow="760" windowWidth="28820" windowHeight="18880" xr2:uid="{5E94D4F8-9F67-BB48-B84E-2D90FAF38DE8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5E94D4F8-9F67-BB48-B84E-2D90FAF38DE8}"/>
   </bookViews>
   <sheets>
     <sheet name="Financements" sheetId="1" r:id="rId1"/>
     <sheet name="Notice" sheetId="2" r:id="rId2"/>
     <sheet name="Data" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,6 +29,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,82 +38,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
-  <si>
-    <t>Ici quelques explications</t>
-  </si>
-  <si>
-    <t>1. Telechager le modèle (ce fichier)</t>
-  </si>
-  <si>
-    <t>3. Enregistrer vos modifications</t>
-  </si>
-  <si>
-    <t>4. Téléverser le fichier modifié dans l'application</t>
-  </si>
-  <si>
-    <t>Attention, en aucun cas vous ne devez modifier l'entête du tableau des prêts, cela casserait l'import des données</t>
-  </si>
-  <si>
-    <t>Préciser l'identité du préteur si vous avez sélectionné 'Autre'</t>
-  </si>
-  <si>
-    <t>EPCI</t>
-  </si>
-  <si>
-    <t>Prêteurs (Ne pas modifier)</t>
-  </si>
-  <si>
-    <t>Montant
-(en €)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+  <si>
+    <t>Numéro
+(caractères alphanuméric)</t>
+  </si>
+  <si>
+    <t>Financement</t>
   </si>
   <si>
     <t>Date d'octroi
 (format dd/mm/yyyy)</t>
-  </si>
-  <si>
-    <t>Numéro
-(caractères alphanuméric)</t>
-  </si>
-  <si>
-    <t>Prêteur
-(choisir dans la liste déroulante)</t>
-  </si>
-  <si>
-    <t>CDC pour le foncier</t>
-  </si>
-  <si>
-    <t>CDC pour le logement</t>
-  </si>
-  <si>
-    <t>2. Modifier à votre guise le fichier</t>
-  </si>
-  <si>
-    <t>5. Vérifier le contenu téléversé dans l'application et enregistrer en cliquant sur le bouton 'Enregistrer et Suivant'</t>
-  </si>
-  <si>
-    <t>ANRU</t>
-  </si>
-  <si>
-    <t>ligne data</t>
-  </si>
-  <si>
-    <t>indiquer l’ensemble des prêts et subventions.</t>
-  </si>
-  <si>
-    <t>Commune et action logement</t>
-  </si>
-  <si>
-    <t>Ville</t>
-  </si>
-  <si>
-    <t>Région</t>
-  </si>
-  <si>
-    <t>Etat</t>
-  </si>
-  <si>
-    <t>Autre/Subventions</t>
   </si>
   <si>
     <r>
@@ -131,6 +68,74 @@
       </rPr>
       <t>Si le prêt est en cours de signature, indiquez une durée indicative</t>
     </r>
+  </si>
+  <si>
+    <t>Montant
+(en €)</t>
+  </si>
+  <si>
+    <t>Prêteur
+(choisir dans la liste déroulante)</t>
+  </si>
+  <si>
+    <t>Préciser l'identité du préteur si vous avez sélectionné 'Autre'</t>
+  </si>
+  <si>
+    <t>Ici quelques explications</t>
+  </si>
+  <si>
+    <t>1. Telechager le modèle (ce fichier)</t>
+  </si>
+  <si>
+    <t>2. Modifier à votre guise le fichier</t>
+  </si>
+  <si>
+    <t>3. Enregistrer vos modifications</t>
+  </si>
+  <si>
+    <t>4. Téléverser le fichier modifié dans l'application</t>
+  </si>
+  <si>
+    <t>5. Vérifier le contenu téléversé dans l'application et enregistrer en cliquant sur le bouton 'Enregistrer et Suivant'</t>
+  </si>
+  <si>
+    <t>Attention, en aucun cas vous ne devez modifier l'entête du tableau des prêts, cela casserait l'import des données</t>
+  </si>
+  <si>
+    <t>indiquer l’ensemble des prêts et subventions.</t>
+  </si>
+  <si>
+    <t>Prêteurs (Ne pas modifier)</t>
+  </si>
+  <si>
+    <t>ligne data</t>
+  </si>
+  <si>
+    <t>Etat</t>
+  </si>
+  <si>
+    <t>CDC pour le foncier</t>
+  </si>
+  <si>
+    <t>CDC pour le logement</t>
+  </si>
+  <si>
+    <t>Région</t>
+  </si>
+  <si>
+    <t>Ville</t>
+  </si>
+  <si>
+    <t>EPCI</t>
+  </si>
+  <si>
+    <t>Commune et action logement</t>
+  </si>
+  <si>
+    <t>ANRU</t>
+  </si>
+  <si>
+    <t>Autre/Subventions</t>
   </si>
 </sst>
 </file>
@@ -328,7 +333,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -347,6 +352,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -463,7 +474,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -759,211 +770,236 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08021C90-1ACF-2A4C-A1B0-58A48A8F7007}">
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.83203125" customWidth="1"/>
+    <col min="1" max="1" width="25.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="20.875" customWidth="1"/>
+    <col min="5" max="5" width="30.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.875" customWidth="1"/>
+    <col min="7" max="7" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
-        <v>10</v>
+    <row r="1" spans="1:7" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
+        <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="24" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="21"/>
+      <c r="G1" s="20" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="23"/>
       <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="19"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C2" s="19"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="21"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="10"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="14"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B3" s="10"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="14"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="9"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="8"/>
       <c r="F4" s="9"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G4" s="9"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="10"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="14"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B5" s="10"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="9"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="8"/>
       <c r="F6" s="9"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G6" s="9"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="14"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B7" s="10"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="9"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="8"/>
       <c r="F8" s="9"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G8" s="9"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="10"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="14"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B9" s="10"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="14"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="9"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="8"/>
       <c r="F10" s="9"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G10" s="9"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="14"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B11" s="10"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="14"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="9"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="8"/>
       <c r="F12" s="9"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G12" s="9"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="10"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="14"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B13" s="10"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="14"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="9"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="8"/>
       <c r="F14" s="9"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G14" s="9"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="10"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="14"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B15" s="10"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="14"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="9"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="8"/>
       <c r="F16" s="9"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G16" s="9"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="14"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B17" s="10"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="14"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="9"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="8"/>
       <c r="F18" s="9"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G18" s="9"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="10"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="14"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B19" s="10"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="14"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="9"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="8"/>
       <c r="F20" s="9"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G20" s="9"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="14"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B21" s="10"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="14"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="9"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="8"/>
       <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="B1:B2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -974,7 +1010,7 @@
           <x14:formula1>
             <xm:f>Data!$A$2:$A$10</xm:f>
           </x14:formula1>
-          <xm:sqref>E3:E22</xm:sqref>
+          <xm:sqref>F3:F22</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -985,50 +1021,50 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{467F41B6-50A5-F34D-9811-537B9541F979}">
   <dimension ref="B2:B10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5" customWidth="1"/>
     <col min="2" max="2" width="67" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="17" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B10" s="17" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1040,65 +1076,65 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4880C39C-0BD9-B447-909B-7F37D33CA805}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E1" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="E2" s="16">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/static/files/financement.xlsx
+++ b/static/files/financement.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29212"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolasoudard/workspace/beta.gouv.fr/apilos/static/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762975EC-3214-904C-AAA5-0B56EA998315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{762975EC-3214-904C-AAA5-0B56EA998315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7178763-0BBA-45B8-86F6-6906562114A1}"/>
   <bookViews>
     <workbookView xWindow="1420" yWindow="760" windowWidth="28820" windowHeight="18880" xr2:uid="{5E94D4F8-9F67-BB48-B84E-2D90FAF38DE8}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Notice" sheetId="2" r:id="rId2"/>
     <sheet name="Data" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,6 +29,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,82 +38,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
-  <si>
-    <t>Ici quelques explications</t>
-  </si>
-  <si>
-    <t>1. Telechager le modèle (ce fichier)</t>
-  </si>
-  <si>
-    <t>3. Enregistrer vos modifications</t>
-  </si>
-  <si>
-    <t>4. Téléverser le fichier modifié dans l'application</t>
-  </si>
-  <si>
-    <t>Attention, en aucun cas vous ne devez modifier l'entête du tableau des prêts, cela casserait l'import des données</t>
-  </si>
-  <si>
-    <t>Préciser l'identité du préteur si vous avez sélectionné 'Autre'</t>
-  </si>
-  <si>
-    <t>EPCI</t>
-  </si>
-  <si>
-    <t>Prêteurs (Ne pas modifier)</t>
-  </si>
-  <si>
-    <t>Montant
-(en €)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+  <si>
+    <t>Numéro
+(caractères alphanuméric)</t>
+  </si>
+  <si>
+    <t>Financement</t>
   </si>
   <si>
     <t>Date d'octroi
 (format dd/mm/yyyy)</t>
-  </si>
-  <si>
-    <t>Numéro
-(caractères alphanuméric)</t>
-  </si>
-  <si>
-    <t>Prêteur
-(choisir dans la liste déroulante)</t>
-  </si>
-  <si>
-    <t>CDC pour le foncier</t>
-  </si>
-  <si>
-    <t>CDC pour le logement</t>
-  </si>
-  <si>
-    <t>2. Modifier à votre guise le fichier</t>
-  </si>
-  <si>
-    <t>5. Vérifier le contenu téléversé dans l'application et enregistrer en cliquant sur le bouton 'Enregistrer et Suivant'</t>
-  </si>
-  <si>
-    <t>ANRU</t>
-  </si>
-  <si>
-    <t>ligne data</t>
-  </si>
-  <si>
-    <t>indiquer l’ensemble des prêts et subventions.</t>
-  </si>
-  <si>
-    <t>Commune et action logement</t>
-  </si>
-  <si>
-    <t>Ville</t>
-  </si>
-  <si>
-    <t>Région</t>
-  </si>
-  <si>
-    <t>Etat</t>
-  </si>
-  <si>
-    <t>Autre/Subventions</t>
   </si>
   <si>
     <r>
@@ -132,6 +69,74 @@
       <t>Si le prêt est en cours de signature, indiquez une durée indicative</t>
     </r>
   </si>
+  <si>
+    <t>Montant
+(en €)</t>
+  </si>
+  <si>
+    <t>Prêteur
+(choisir dans la liste déroulante)</t>
+  </si>
+  <si>
+    <t>Préciser l'identité du préteur si vous avez sélectionné 'Autre'</t>
+  </si>
+  <si>
+    <t>Ici quelques explications</t>
+  </si>
+  <si>
+    <t>1. Telechager le modèle (ce fichier)</t>
+  </si>
+  <si>
+    <t>2. Modifier à votre guise le fichier</t>
+  </si>
+  <si>
+    <t>3. Enregistrer vos modifications</t>
+  </si>
+  <si>
+    <t>4. Téléverser le fichier modifié dans l'application</t>
+  </si>
+  <si>
+    <t>5. Vérifier le contenu téléversé dans l'application et enregistrer en cliquant sur le bouton 'Enregistrer et Suivant'</t>
+  </si>
+  <si>
+    <t>Attention, en aucun cas vous ne devez modifier l'entête du tableau des prêts, cela casserait l'import des données</t>
+  </si>
+  <si>
+    <t>indiquer l’ensemble des prêts et subventions.</t>
+  </si>
+  <si>
+    <t>Prêteurs (Ne pas modifier)</t>
+  </si>
+  <si>
+    <t>ligne data</t>
+  </si>
+  <si>
+    <t>Etat</t>
+  </si>
+  <si>
+    <t>CDC pour le foncier</t>
+  </si>
+  <si>
+    <t>CDC pour le logement</t>
+  </si>
+  <si>
+    <t>Région</t>
+  </si>
+  <si>
+    <t>Ville</t>
+  </si>
+  <si>
+    <t>EPCI</t>
+  </si>
+  <si>
+    <t>Commune et action logement</t>
+  </si>
+  <si>
+    <t>ANRU</t>
+  </si>
+  <si>
+    <t>Autre/Subventions</t>
+  </si>
 </sst>
 </file>
 
@@ -140,7 +145,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ [$€-40C]"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -328,7 +333,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -347,6 +352,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -394,6 +405,13 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -403,13 +421,6 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -453,7 +464,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{60458129-C213-8741-80B4-B15A740996D3}" name="preteurs" displayName="preteurs" ref="A1:A10" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2" totalsRowBorderDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{60458129-C213-8741-80B4-B15A740996D3}" name="preteurs" displayName="preteurs" ref="A1:A10" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="2" tableBorderDxfId="3" totalsRowBorderDxfId="1">
   <autoFilter ref="A1:A10" xr:uid="{60458129-C213-8741-80B4-B15A740996D3}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{68B921AF-0801-1140-A800-5EFE7005DB88}" name="Prêteurs (Ne pas modifier)" dataDxfId="0"/>
@@ -463,9 +474,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -503,7 +514,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -609,7 +620,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -751,7 +762,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -759,211 +770,237 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08021C90-1ACF-2A4C-A1B0-58A48A8F7007}">
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="30.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.83203125" customWidth="1"/>
+    <col min="1" max="1" width="25.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="20.875" customWidth="1"/>
+    <col min="5" max="5" width="30.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.875" customWidth="1"/>
+    <col min="7" max="7" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
-        <v>10</v>
+    <row r="1" spans="1:7" ht="72" customHeight="1">
+      <c r="A1" s="22" t="s">
+        <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="24" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="21"/>
+      <c r="G1" s="20" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.75">
+      <c r="A2" s="23"/>
       <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="19"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C2" s="19"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="21"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75">
       <c r="A3" s="10"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="14"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B3" s="10"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="14"/>
+    </row>
+    <row r="4" spans="1:7" ht="15.75">
       <c r="A4" s="5"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="9"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="8"/>
       <c r="F4" s="9"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G4" s="9"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.75">
       <c r="A5" s="10"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="14"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B5" s="10"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.75">
       <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="9"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="8"/>
       <c r="F6" s="9"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G6" s="9"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.75">
       <c r="A7" s="10"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="14"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B7" s="10"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.75">
       <c r="A8" s="5"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="9"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="8"/>
       <c r="F8" s="9"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G8" s="9"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.75">
       <c r="A9" s="10"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="14"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B9" s="10"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="14"/>
+    </row>
+    <row r="10" spans="1:7" ht="15.75">
       <c r="A10" s="5"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="9"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="8"/>
       <c r="F10" s="9"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G10" s="9"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.75">
       <c r="A11" s="10"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="14"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B11" s="10"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="14"/>
+    </row>
+    <row r="12" spans="1:7" ht="15.75">
       <c r="A12" s="5"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="9"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="8"/>
       <c r="F12" s="9"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G12" s="9"/>
+    </row>
+    <row r="13" spans="1:7" ht="15.75">
       <c r="A13" s="10"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="14"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B13" s="10"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="14"/>
+    </row>
+    <row r="14" spans="1:7" ht="15.75">
       <c r="A14" s="5"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="9"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="8"/>
       <c r="F14" s="9"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G14" s="9"/>
+    </row>
+    <row r="15" spans="1:7" ht="15.75">
       <c r="A15" s="10"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="14"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B15" s="10"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="14"/>
+    </row>
+    <row r="16" spans="1:7" ht="15.75">
       <c r="A16" s="5"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="9"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="8"/>
       <c r="F16" s="9"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G16" s="9"/>
+    </row>
+    <row r="17" spans="1:7" ht="15.75">
       <c r="A17" s="10"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="14"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B17" s="10"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="14"/>
+    </row>
+    <row r="18" spans="1:7" ht="15.75">
       <c r="A18" s="5"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="9"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="8"/>
       <c r="F18" s="9"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G18" s="9"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.75">
       <c r="A19" s="10"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="14"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B19" s="10"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="14"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.75">
       <c r="A20" s="5"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="9"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="8"/>
       <c r="F20" s="9"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G20" s="9"/>
+    </row>
+    <row r="21" spans="1:7" ht="15.75">
       <c r="A21" s="10"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="14"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B21" s="10"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="14"/>
+    </row>
+    <row r="22" spans="1:7" ht="15.75">
       <c r="A22" s="5"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="9"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-    </row>
+      <c r="G22" s="9"/>
+    </row>
+    <row r="23" spans="1:7" ht="15.75"/>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="B1:B2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -974,7 +1011,7 @@
           <x14:formula1>
             <xm:f>Data!$A$2:$A$10</xm:f>
           </x14:formula1>
-          <xm:sqref>E3:E22</xm:sqref>
+          <xm:sqref>F3:F22</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -985,50 +1022,50 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{467F41B6-50A5-F34D-9811-537B9541F979}">
   <dimension ref="B2:B10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="6.5" customWidth="1"/>
     <col min="2" max="2" width="67" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:2">
       <c r="B2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
       <c r="B4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" s="17" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B10" s="17" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1040,65 +1077,65 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4880C39C-0BD9-B447-909B-7F37D33CA805}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="42.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E1" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="E2" s="16">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
